--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrRepo003MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrRepo003MTM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\joyinwork\bs2.1.2\2.1.2\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
   <si>
     <t>委托开始日</t>
   </si>
@@ -279,6 +279,10 @@
   </si>
   <si>
     <t>最低成交金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期限品种</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -663,29 +667,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.125" customWidth="1"/>
     <col min="2" max="6" width="14.625" customWidth="1"/>
     <col min="7" max="7" width="10.25" customWidth="1"/>
     <col min="8" max="13" width="14.625" customWidth="1"/>
-    <col min="14" max="14" width="18.25" customWidth="1"/>
-    <col min="15" max="17" width="14.625" customWidth="1"/>
-    <col min="19" max="19" width="15.125" customWidth="1"/>
-    <col min="20" max="20" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="18.25" customWidth="1"/>
+    <col min="16" max="18" width="14.625" customWidth="1"/>
+    <col min="20" max="20" width="15.125" customWidth="1"/>
+    <col min="21" max="21" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -729,24 +733,27 @@
         <v>50</v>
       </c>
       <c r="O2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" t="s">
         <v>51</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>8</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>9</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>52</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>56</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>54</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrRepo003MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrRepo003MTM.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14535" windowHeight="3675"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
     <sheet name="参考格式" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="82">
   <si>
     <t>委托开始日</t>
   </si>
@@ -283,6 +283,14 @@
   </si>
   <si>
     <t>期限品种</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H04:质押式回购</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请输入账号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -783,12 +791,6 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>参考格式!$H$3:$H$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>H3:H1002</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>参考格式!$J$3:$J$5</xm:f>
           </x14:formula1>
           <xm:sqref>J3:J1002</xm:sqref>
@@ -798,6 +800,12 @@
             <xm:f>参考格式!$M$3:$M$5</xm:f>
           </x14:formula1>
           <xm:sqref>M3:M1002</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>参考格式!$H$3:$H$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>H1:H1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -917,6 +925,9 @@
       <c r="M3" t="s">
         <v>61</v>
       </c>
+      <c r="P3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.15">
       <c r="E4" t="s">
@@ -944,6 +955,9 @@
       </c>
       <c r="G5" t="s">
         <v>64</v>
+      </c>
+      <c r="H5" t="s">
+        <v>80</v>
       </c>
       <c r="J5" t="s">
         <v>44</v>
